--- a/entertainment_forms/024_foundation_shade_quiz--entertainment_forms.xlsx
+++ b/entertainment_forms/024_foundation_shade_quiz--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1130,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C253"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>fair with a slightly yellow tint</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_red_tint</t>
+          <t>fair with a slightly yellow tint and a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>olive_with_a_slightly_yellow_tint</t>
+          <t>olive with a slightly yellow tint</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>olive_with_a_slightly_yellow_tint_and_a_slightly_red_tint</t>
+          <t>olive with a slightly yellow tint and a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cool_with_a_slightly_red_tint</t>
+          <t>cool with a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>warm_with_a_slightly_red_tint</t>
+          <t>warm with a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>combination with a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_yellow_tint</t>
+          <t>combination with a slightly yellow tint</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>fair with a slightly yellow tint</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_red_tint</t>
+          <t>fair with a slightly yellow tint and a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_brown_tint</t>
+          <t>fair with a slightly yellow tint and a slightly brown tint</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_red_tint</t>
+          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_green_tint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_red_tint</t>
+          <t>fair with a slightly yellow tint and a slightly green tint</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_green_tint</t>
+          <t>fair_with_a_slightly_red_tint</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_green_tint</t>
+          <t>fair with a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_brown_tint</t>
+          <t>fair_with_a_slightly_red_tint_and_a_slightly_yellow_tint</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_brown_tint</t>
+          <t>fair with a slightly red tint and a slightly yellow tint</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_red_tint</t>
+          <t>fair_with_a_slightly_red_tint_and_a_slightly_brown_tint</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_red_tint</t>
+          <t>fair with a slightly red tint and a slightly brown tint</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_red_tint_and_a_slightly_yellow_tint</t>
+          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_white_tint</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_red_tint_and_a_slightly_yellow_tint</t>
+          <t>fair with a slightly yellow tint and a slightly white tint</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_red_tint_and_a_slightly_brown_tint</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_red_tint_and_a_slightly_brown_tint</t>
+          <t>olive</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_white_tint</t>
+          <t>olive_with_a_slightly_red_tint</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_white_tint</t>
+          <t>olive with a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>combination</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_white_tint</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_white_tint</t>
+          <t>cool</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>combination_with_a_slightly_red_tint</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>combination with a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>combination_with_a_slightly_yellow_tint</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>combination with a slightly yellow tint</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>olive_with_a_slightly_red_tint</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>olive_with_a_slightly_red_tint</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>warm_with_a_slightly_red_tint</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>warm with a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_white_tint</t>
+          <t>cool_with_a_slightly_red_tint</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_white_tint</t>
+          <t>cool with a slightly red tint</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>cool_with_a_slightly_yellow_tint</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>cool with a slightly yellow tint</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>combination_with_a_slightly_white_tint</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>combination with a slightly white tint</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>combination_with_a_slightly_brown_tint</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>combination with a slightly brown tint</t>
         </is>
       </c>
     </row>
@@ -1792,1940 +1792,1940 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_red_tint</t>
+          <t>combination_with_a_slightly_green_tint</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_red_tint</t>
+          <t>combination with a slightly green tint</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_brown_tint</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_brown_tint</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>combination</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>combination</t>
+          <t>cool</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>cool</t>
+          <t>cool_with_a_slightly_red_tint</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>cool</t>
+          <t>cool with a slightly red tint</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_yellow_tint</t>
+          <t>warm_with_a_slightly_white_tint</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_yellow_tint</t>
+          <t>warm with a slightly white tint</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fair</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>combination</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>warm_with_a_slightly_red_tint</t>
+          <t>combination_with_a_slightly_red_tint</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>warm_with_a_slightly_red_tint</t>
+          <t>combination with a slightly red tint</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>combination_with_a_slightly_white_tint</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint</t>
+          <t>combination with a slightly white tint</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_foundation_color_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_white_tint</t>
+          <t>combination_with_a_slightly_brown_tint</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>fair_with_a_slightly_yellow_tint_and_a_slightly_white_tint</t>
+          <t>combination with a slightly brown tint</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_eye_shape_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>cool_with_a_slightly_red_tint</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>cool_with_a_slightly_red_tint</t>
+          <t>round</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_eye_shape_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>cool_with_a_slightly_yellow_tint</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>cool_with_a_slightly_yellow_tint</t>
+          <t>oval</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_eye_shape_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>combination</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>combination</t>
+          <t>heart</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_eye_shape_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>square</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_eye_shape_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_yellow_tint</t>
+          <t>almond</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_yellow_tint</t>
+          <t>almond</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_eye_shape_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_white_tint</t>
+          <t>heart_with_a_pointy_tip</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_white_tint</t>
+          <t>heart with a pointy tip</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_eye_shape_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_brown_tint</t>
+          <t>almond_with_a_pointed_tip</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_brown_tint</t>
+          <t>almond with a pointed tip</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_yellow_tint</t>
+          <t>normal_with_a_slightly_high_cheek_bone</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_yellow_tint</t>
+          <t>normal with a slightly high cheek bone</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_white_tint</t>
+          <t>normal_with_a_slightly_low_cheek_bone</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_white_tint</t>
+          <t>normal with a slightly low cheek bone</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_brown_tint</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_brown_tint</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_green_tint</t>
+          <t>high_with_a_slightly_high_cheek_bone</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_green_tint</t>
+          <t>high with a slightly high cheek bone</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_type_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>high_with_a_slightly_low_cheek_bone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>high with a slightly low cheek bone</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>high_with_a_high_cheek_bone</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>high with a high cheek bone</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>cool</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>cool</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>cool_with_a_slightly_red_tint</t>
+          <t>low_with_a_slightly_high_cheek_bone</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>cool_with_a_slightly_red_tint</t>
+          <t>low with a slightly high cheek bone</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>low_with_a_slightly_low_cheek_bone</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>low with a slightly low cheek bone</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>warm_with_a_slightly_white_tint</t>
+          <t>low_with_a_low_cheek_bone</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>warm_with_a_slightly_white_tint</t>
+          <t>low with a low cheek bone</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_facial_structure_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>high_with_a_low_cheek_bone</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>high with a low cheek bone</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_face_shape_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>combination</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>combination</t>
+          <t>round</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_face_shape_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_red_tint</t>
+          <t>oval</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_face_shape_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_white_tint</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_white_tint</t>
+          <t>square</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_foundation_color_choices</t>
+          <t>foundation_shade_quiz_face_shape_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_brown_tint</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>combination_with_a_slightly_brown_tint</t>
+          <t>heart</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_eye_shape_choices</t>
+          <t>foundation_shade_quiz_face_shape_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>almond</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>almond</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_eye_shape_choices</t>
+          <t>foundation_shade_quiz_face_shape_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>diamond</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_eye_shape_choices</t>
+          <t>foundation_shade_quiz_face_shape_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>hexagonal</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>hexagonal</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_eye_shape_choices</t>
+          <t>foundation_shade_quiz_face_shape_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>heart_with_a_pointy_tip</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>heart with a pointy tip</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_eye_shape_choices</t>
+          <t>foundation_shade_quiz_face_shape_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>almond</t>
+          <t>almond_with_a_pointed_tip</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>almond</t>
+          <t>almond with a pointed tip</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_eye_shape_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>heart_with_a_pointy_tip</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>heart_with_a_pointy_tip</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_eye_shape_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>almond_with_a_pointed_tip</t>
+          <t>normal_with_a_minor_acne</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>almond_with_a_pointed_tip</t>
+          <t>normal with a minor acne</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>normal_with_a_minor_redness</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>normal with a minor redness</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>normal_with_a_slightly_high_cheek_bone</t>
+          <t>normal_with_a_minor_blackhead</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>normal_with_a_slightly_high_cheek_bone</t>
+          <t>normal with a minor blackhead</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>normal_with_a_slightly_low_cheek_bone</t>
+          <t>normal_with_a_minor_whitehead</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>normal_with_a_slightly_low_cheek_bone</t>
+          <t>normal with a minor whitehead</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>normal_with_a_minor_olive_tone</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>normal with a minor olive tone</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>high_with_a_slightly_high_cheek_bone</t>
+          <t>normal_with_a_minor_yellow_tone</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>high_with_a_slightly_high_cheek_bone</t>
+          <t>normal with a minor yellow tone</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>high_with_a_slightly_low_cheek_bone</t>
+          <t>normal_with_a_minor_green_tone</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>high_with_a_slightly_low_cheek_bone</t>
+          <t>normal with a minor green tone</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>high_with_a_high_cheek_bone</t>
+          <t>normal_with_a_minor_brown_tone</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>high_with_a_high_cheek_bone</t>
+          <t>normal with a minor brown tone</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>normal_with_a_minor_purple_tone</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>normal with a minor purple tone</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>low_with_a_slightly_high_cheek_bone</t>
+          <t>normal_with_a_minor_black_tone</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>low_with_a_slightly_high_cheek_bone</t>
+          <t>normal with a minor black tone</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>low_with_a_slightly_low_cheek_bone</t>
+          <t>normal_with_a_minor_white_tone</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>low_with_a_slightly_low_cheek_bone</t>
+          <t>normal with a minor white tone</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>low_with_a_low_cheek_bone</t>
+          <t>normal_with_a_minor_red_tone</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>low_with_a_low_cheek_bone</t>
+          <t>normal with a minor red tone</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_facial_structure_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>high_with_a_low_cheek_bone</t>
+          <t>normal_with_a_minor_pink_tone</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>high_with_a_low_cheek_bone</t>
+          <t>normal with a minor pink tone</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_face_shape_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>normal_with_a_minor_grey_tone</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>normal with a minor grey tone</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_face_shape_choices</t>
+          <t>foundation_shade_quiz_skin_condition_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>normal_with_a_minor_blue_tone</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>normal with a minor blue tone</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_face_shape_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_face_shape_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>normal_with_a_minor_acne</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>normal with a minor acne</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_face_shape_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>almond</t>
+          <t>normal_with_a_minor_redness</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>almond</t>
+          <t>normal with a minor redness</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_face_shape_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>normal_with_a_minor_blackhead</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>normal with a minor blackhead</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_face_shape_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>hexagonal</t>
+          <t>normal_with_a_minor_whitehead</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>hexagonal</t>
+          <t>normal with a minor whitehead</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_face_shape_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>heart_with_a_pointy_tip</t>
+          <t>normal_with_a_minor_olive_tone</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>heart_with_a_pointy_tip</t>
+          <t>normal with a minor olive tone</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_face_shape_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>almond_with_a_pointed_tip</t>
+          <t>normal_with_a_minor_yellow_tone</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>almond_with_a_pointed_tip</t>
+          <t>normal with a minor yellow tone</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>normal_with_a_minor_green_tone</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>normal with a minor green tone</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_acne</t>
+          <t>normal_with_a_minor_brown_tone</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_acne</t>
+          <t>normal with a minor brown tone</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_redness</t>
+          <t>normal_with_a_minor_purple_tone</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_redness</t>
+          <t>normal with a minor purple tone</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blackhead</t>
+          <t>normal_with_a_minor_black_tone</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blackhead</t>
+          <t>normal with a minor black tone</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_whitehead</t>
+          <t>normal_with_a_minor_white_tone</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_whitehead</t>
+          <t>normal with a minor white tone</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_olive_tone</t>
+          <t>normal_with_a_minor_red_tone</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_olive_tone</t>
+          <t>normal with a minor red tone</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal_with_a_minor_pink_tone</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal with a minor pink tone</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal_with_a_minor_grey_tone</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal with a minor grey tone</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_pigmentation_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal_with_a_minor_blue_tone</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal with a minor blue tone</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal_with_a_minor_acne</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal with a minor acne</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal_with_a_minor_blackhead</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal with a minor blackhead</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal_with_a_minor_whitehead</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal with a minor whitehead</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_pink_tone</t>
+          <t>normal_with_a_minor_olive_tone</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_pink_tone</t>
+          <t>normal with a minor olive tone</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal_with_a_minor_yellow_tone</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal with a minor yellow tone</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blue_tone</t>
+          <t>normal_with_a_minor_green_tone</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blue_tone</t>
+          <t>normal with a minor green tone</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal_with_a_minor_brown_tone</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal with a minor brown tone</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal_with_a_minor_purple_tone</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal with a minor purple tone</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal_with_a_minor_black_tone</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal with a minor black tone</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal_with_a_minor_white_tone</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal with a minor white tone</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal_with_a_minor_red_tone</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal with a minor red tone</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal_with_a_minor_grey_tone</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal with a minor grey tone</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal_with_a_minor_acne</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal with a minor acne</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal_with_a_minor_blackhead</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal with a minor blackhead</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_skin_condition_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal_with_a_minor_whitehead</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal with a minor whitehead</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>normal_with_a_minor_olive_tone</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>normal with a minor olive tone</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_acne</t>
+          <t>normal_with_a_minor_yellow_tone</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_acne</t>
+          <t>normal with a minor yellow tone</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_redness</t>
+          <t>normal_with_a_minor_green_tone</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_redness</t>
+          <t>normal with a minor green tone</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blackhead</t>
+          <t>normal_with_a_minor_brown_tone</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blackhead</t>
+          <t>normal with a minor brown tone</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_whitehead</t>
+          <t>normal_with_a_minor_purple_tone</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_whitehead</t>
+          <t>normal with a minor purple tone</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_olive_tone</t>
+          <t>normal_with_a_minor_black_tone</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_olive_tone</t>
+          <t>normal with a minor black tone</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal_with_a_minor_white_tone</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal with a minor white tone</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal_with_a_minor_red_tone</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal with a minor red tone</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_acne_scars_2_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal_with_a_minor_grey_tone</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal with a minor grey tone</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal_with_a_minor_curly</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal with a minor curly</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal_with_a_minor_wavy</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal with a minor wavy</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal_with_a_minor_straight</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal with a minor straight</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_pink_tone</t>
+          <t>normal_with_a_minor_blonde</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_pink_tone</t>
+          <t>normal with a minor blonde</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal_with_a_minor_brown</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal with a minor brown</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blue_tone</t>
+          <t>normal_with_a_minor_black</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blue_tone</t>
+          <t>normal with a minor black</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal_with_a_minor_red</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal with a minor red</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal_with_a_minor_purple</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal with a minor purple</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal_with_a_minor_grey</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal with a minor grey</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_type_choices</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal_with_a_minor_green</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal with a minor green</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_length_choices</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_length_choices</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal_with_a_minor_long</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal with a minor long</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_length_choices</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal_with_a_minor_medium</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal with a minor medium</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_length_choices</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal_with_a_minor_short</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal with a minor short</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_length_choices</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal_with_a_minor_very_long</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal with a minor very long</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_pigmentation_choices</t>
+          <t>foundation_shade_quiz_hair_length_choices</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal_with_a_minor_very_short</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal with a minor very short</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3742,1700 +3742,493 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_acne</t>
+          <t>normal_with_a_minor_straight</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_acne</t>
+          <t>normal with a minor straight</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blackhead</t>
+          <t>normal_with_a_minor_wavy</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blackhead</t>
+          <t>normal with a minor wavy</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_whitehead</t>
+          <t>normal_with_a_minor_curly</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_whitehead</t>
+          <t>normal with a minor curly</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_olive_tone</t>
+          <t>normal_with_a_minor_pony</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_olive_tone</t>
+          <t>normal with a minor pony</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal_with_a_minor_blonde</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal with a minor blonde</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal_with_a_minor_brown</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal with a minor brown</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal_with_a_minor_black</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal with a minor black</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal_with_a_minor_red</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal with a minor red</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal_with_a_minor_purple</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal with a minor purple</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal_with_a_minor_grey</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal with a minor grey</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_texture_choices</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal_with_a_minor_green</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal with a minor green</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_color_choices</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_color_choices</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal_with_a_minor_black</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal with a minor black</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_color_choices</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal_with_a_minor_blonde</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal with a minor blonde</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_color_choices</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal_with_a_minor_brown</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_white_tone</t>
+          <t>normal with a minor brown</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_color_choices</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal_with_a_minor_grey</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal with a minor grey</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_color_choices</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal_with_a_minor_green</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_red_tone</t>
+          <t>normal with a minor green</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_color_choices</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal_with_a_minor_purple</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_grey_tone</t>
+          <t>normal with a minor purple</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_color_choices</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal_with_a_minor_red</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal with a minor red</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_choices</t>
+          <t>foundation_shade_quiz_hair_color_2_choices</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_black_tone</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
+          <t>foundation_shade_quiz_hair_color_2_choices</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>normal_with_a_minor_black</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>normal with a minor black</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
+          <t>foundation_shade_quiz_hair_color_2_choices</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_acne</t>
+          <t>normal_with_a_minor_blonde</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_acne</t>
+          <t>normal with a minor blonde</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
+          <t>foundation_shade_quiz_hair_color_2_choices</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blackhead</t>
+          <t>normal_with_a_minor_brown</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_blackhead</t>
+          <t>normal with a minor brown</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
+          <t>foundation_shade_quiz_hair_color_2_choices</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_whitehead</t>
+          <t>normal_with_a_minor_grey</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_whitehead</t>
+          <t>normal with a minor grey</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
+          <t>foundation_shade_quiz_hair_color_2_choices</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_olive_tone</t>
+          <t>normal_with_a_minor_green</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_olive_tone</t>
+          <t>normal with a minor green</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
+          <t>foundation_shade_quiz_hair_color_2_choices</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal_with_a_minor_purple</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_yellow_tone</t>
+          <t>normal with a minor purple</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
+          <t>foundation_shade_quiz_important_question_5_choices</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_green_tone</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
+          <t>foundation_shade_quiz_important_question_5_choices</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal_with_a_minor_sodium-lauryr-sulfate</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_brown_tone</t>
+          <t>normal with a minor sodium-lauryr-sulfate</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
+          <t>foundation_shade_quiz_important_question_5_choices</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
+          <t>normal_with_a_minor_olive</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>normal_with_a_minor_purple_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black_tone</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_white_tone</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_white_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red_tone</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey_tone</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green_tone</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black_tone</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_white_tone</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_white_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_yellow_tone</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_yellow_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red_tone</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey_tone</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green_tone</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_acne_scars_2_choices</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black_tone</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black_tone</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_curly</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_curly</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_wavy</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_wavy</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_straight</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_straight</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_brown</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_brown</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_purple</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_purple</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_type_choices</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_length_choices</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_length_choices</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_long</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_long</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_length_choices</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_medium</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_length_choices</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_short</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_short</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_length_choices</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_very_long</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_very_long</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_length_choices</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_very_short</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_very_short</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_straight</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_straight</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_wavy</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_wavy</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_curly</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_curly</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_pony</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_pony</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_brown</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_brown</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_purple</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_purple</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_texture_choices</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_brown</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_brown</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_purple</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_purple</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_red</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_choices</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_brown</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_brown</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_grey</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_green</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_purple</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_purple</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_black</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_hair_color_2_choices</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_blonde</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_important_question_5_choices</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_important_question_5_choices</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_sodium-lauryr-sulfate</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_sodium-lauryr-sulfate</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_important_question_5_choices</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_olive</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_olive</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_important_question_5_choices</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_sodium-lauryr-sulfate</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_sodium-lauryr-sulfate</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_important_question_5_choices</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_olive</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_olive</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_important_question_5_choices</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_olive</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_olive</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>foundation_shade_quiz_important_question_5_choices</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_olive</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>normal_with_a_minor_olive</t>
+          <t>normal with a minor olive</t>
         </is>
       </c>
     </row>
